--- a/inputs/acceptance_cases/stage2_absolute_unknown_cluster.xlsx
+++ b/inputs/acceptance_cases/stage2_absolute_unknown_cluster.xlsx
@@ -479,7 +479,7 @@
         <v>44569.3125</v>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -490,7 +490,7 @@
         <v>44569.32291666666</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         <v>44569.34375</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -534,7 +534,7 @@
         <v>44569.36458333334</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -556,7 +556,7 @@
         <v>44569.38541666666</v>
       </c>
       <c r="C11" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -567,7 +567,7 @@
         <v>44569.39583333334</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -600,7 +600,7 @@
         <v>44569.42708333334</v>
       </c>
       <c r="C15" t="n">
-        <v>5.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -611,7 +611,7 @@
         <v>44569.4375</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>32.99999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -622,7 +622,7 @@
         <v>44569.44791666666</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -633,7 +633,7 @@
         <v>44569.45833333334</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -644,7 +644,7 @@
         <v>44569.46875</v>
       </c>
       <c r="C19" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -655,7 +655,7 @@
         <v>44569.47916666666</v>
       </c>
       <c r="C20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
